--- a/data/trans_orig/IP31KM08_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM08_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>886</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3124</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,18%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>810</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3937</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3515</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1067</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3754</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>431</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>4808</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>70590</t>
+          <t>59377</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67463</t>
+          <t>57139</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71400</t>
+          <t>60263</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>73540</t>
+          <t>54217</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70853</t>
+          <t>51407</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>144130</t>
+          <t>113594</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>140669</t>
+          <t>110378</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145522</t>
+          <t>114755</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>40750</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>31142</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>52057</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>35,45%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>27,09%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>45,29%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>35228</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15746</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>49415</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>28,04%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>12,53%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>39,33%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>44536</t>
+          <t>35275</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33701</t>
+          <t>26997</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56296</t>
+          <t>42785</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>79764</t>
+          <t>76025</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53807</t>
+          <t>62760</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>95980</t>
+          <t>88851</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>41,46%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>74201</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>62894</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>83809</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>64,55%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>54,71%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>72,91%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>90421</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>76234</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>109903</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>71,96%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>60,67%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>87,47%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>81887</t>
+          <t>64058</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>70127</t>
+          <t>56548</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92722</t>
+          <t>72336</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>172307</t>
+          <t>138259</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>156091</t>
+          <t>125433</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>198264</t>
+          <t>151524</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>70,71%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25788</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20363</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>31294</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>45,01%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>35,54%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>54,62%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>26255</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>19997</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>32163</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>47,26%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>36,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>57,9%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>29078</t>
+          <t>25293</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22303</t>
+          <t>20167</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35693</t>
+          <t>30559</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>55333</t>
+          <t>51082</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46692</t>
+          <t>42903</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64622</t>
+          <t>59708</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,59%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>31511</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>26005</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>36936</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>54,99%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>45,38%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>64,46%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>29297</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>23389</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>35555</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>52,74%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>42,1%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>64,0%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>35555</t>
+          <t>28819</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28940</t>
+          <t>23553</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42330</t>
+          <t>33945</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>64852</t>
+          <t>60329</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>55563</t>
+          <t>51703</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73493</t>
+          <t>68508</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,49%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25956</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>16018</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>36302</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>37,18%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>22,94%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>52,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>31737</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>25144</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>40051</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>45,55%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>36,08%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>57,48%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26904</t>
+          <t>31699</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15277</t>
+          <t>24122</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38263</t>
+          <t>39088</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>58642</t>
+          <t>57655</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43472</t>
+          <t>44074</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71481</t>
+          <t>71682</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>51,1%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>43860</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>33514</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>53798</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>62,82%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>48,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>77,06%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>37945</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>29631</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>44538</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>54,45%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>42,52%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>63,92%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>48463</t>
+          <t>38763</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>31374</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60090</t>
+          <t>46340</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>86407</t>
+          <t>82623</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>73568</t>
+          <t>68596</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>101577</t>
+          <t>96204</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>68,58%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15656</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11524</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>20580</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>39,56%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>29,12%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>52,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>11411</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7343</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15720</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>33,36%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>21,47%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>45,96%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16950</t>
+          <t>11892</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12038</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22052</t>
+          <t>16480</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>27547</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21742</t>
+          <t>21522</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>34178</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>45,6%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>23923</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>18999</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>28055</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>60,44%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>48,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>70,88%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>22789</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>18480</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>26857</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>66,64%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>54,04%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>78,53%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>23769</t>
+          <t>23478</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18667</t>
+          <t>18890</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28681</t>
+          <t>27310</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>46558</t>
+          <t>47402</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40225</t>
+          <t>40771</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53177</t>
+          <t>53427</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>71,29%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,67 +2440,67 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>12978</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9946</t>
+          <t>8505</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
+          <t>18217</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>27,49%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>18,02%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>38,59%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>14159</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>9609</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
           <t>19109</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>31,84%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>22,46%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>43,14%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>14669</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>9998</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>20440</t>
-        </is>
-      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>28773</t>
+          <t>27137</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21922</t>
+          <t>21006</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36065</t>
+          <t>34311</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>37,5%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>34231</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>28992</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>38704</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>72,51%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>61,41%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>81,98%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>30186</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>25181</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>34344</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>68,16%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>56,86%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>77,54%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>39113</t>
+          <t>30127</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33342</t>
+          <t>25177</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43784</t>
+          <t>34677</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>69299</t>
+          <t>64358</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>62007</t>
+          <t>57184</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>76150</t>
+          <t>70489</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,04%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>77070</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>64801</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>87258</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>54,83%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>46,1%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>62,07%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>64611</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>54417</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>73676</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>52,23%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>43,99%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>59,56%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>87404</t>
+          <t>61091</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>73418</t>
+          <t>50939</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>100602</t>
+          <t>70502</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>152015</t>
+          <t>138162</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>134887</t>
+          <t>122672</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>168171</t>
+          <t>151234</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>57,64%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>63501</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>53313</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>75770</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>45,17%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>37,93%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>53,9%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>59085</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>50020</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>69279</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>47,77%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>40,44%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>56,01%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>67640</t>
+          <t>60731</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>54442</t>
+          <t>51320</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>81626</t>
+          <t>70883</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>126725</t>
+          <t>124232</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>110569</t>
+          <t>111160</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>143853</t>
+          <t>139722</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>53,25%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>115181</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>104605</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>125219</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>73,3%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>66,57%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>79,69%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>97933</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>90107</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>105443</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>76,11%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>70,03%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>81,95%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>113169</t>
+          <t>106841</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>102953</t>
+          <t>96733</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>122423</t>
+          <t>114387</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>211101</t>
+          <t>222022</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>195683</t>
+          <t>209419</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>222811</t>
+          <t>235314</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>79,76%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>41955</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>31917</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>52531</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>26,7%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>20,31%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>33,43%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>30732</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>23222</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>38558</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>23,89%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>18,05%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>29,97%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>40990</t>
+          <t>31059</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>31736</t>
+          <t>23513</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51206</t>
+          <t>41167</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>71722</t>
+          <t>73014</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>60012</t>
+          <t>59722</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>87140</t>
+          <t>85617</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>29,02%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>314265</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>289722</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>339438</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>45,76%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>42,18%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>49,42%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>406</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>282089</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>240513</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>305116</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>43,19%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>36,82%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>46,72%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>333776</t>
+          <t>286956</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>305651</t>
+          <t>265036</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>361634</t>
+          <t>307614</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>615865</t>
+          <t>601221</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>570122</t>
+          <t>565196</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>653213</t>
+          <t>633148</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>48,52%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>372559</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>347386</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>397102</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>54,24%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>50,58%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>57,82%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>371045</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>348018</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>412621</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>56,81%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>53,28%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>63,18%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>410957</t>
+          <t>331252</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>383099</t>
+          <t>310594</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>439082</t>
+          <t>353172</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>782002</t>
+          <t>703810</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>744654</t>
+          <t>671883</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>827745</t>
+          <t>739835</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>56,69%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
